--- a/artfynd/A 30441-2019 artfynd.xlsx
+++ b/artfynd/A 30441-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126405236</v>
       </c>
       <c r="B2" t="n">
-        <v>110443</v>
+        <v>110452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30441-2019 artfynd.xlsx
+++ b/artfynd/A 30441-2019 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126978583</v>
       </c>
       <c r="B3" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Larsson, Hannes Byström</t>
+          <t>Hannes Byström, Anton Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>126978564</v>
       </c>
       <c r="B4" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126978562</v>
       </c>
       <c r="B5" t="n">
-        <v>100450</v>
+        <v>100525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
